--- a/data/trans_bre/P74B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,52; 79,58</t>
+          <t>71,74; 79,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,19; 65,48</t>
+          <t>55,14; 65,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54,66; 65,53</t>
+          <t>54,33; 65,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455,33; 743,0</t>
+          <t>457,73; 734,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>234,13; 392,67</t>
+          <t>236,43; 379,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>239,24; 410,88</t>
+          <t>233,54; 408,51</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,11; 68,36</t>
+          <t>51,77; 68,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,42; 48,26</t>
+          <t>34,24; 47,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,21; 50,76</t>
+          <t>38,63; 50,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1303,42; 3917,04</t>
+          <t>1277,82; 3545,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>401,05; 898,02</t>
+          <t>397,89; 857,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>379,21; 686,03</t>
+          <t>374,33; 701,92</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,45; 90,68</t>
+          <t>54,16; 90,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,58; 62,54</t>
+          <t>28,0; 61,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,39; 49,97</t>
+          <t>18,78; 49,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>576,09; 2750,38</t>
+          <t>543,28; 2739,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>138,53; 907,4</t>
+          <t>150,19; 948,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96,94; 490,82</t>
+          <t>99,15; 473,64</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,91; 78,22</t>
+          <t>71,58; 78,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,34; 58,99</t>
+          <t>51,81; 59,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,56; 57,03</t>
+          <t>49,88; 57,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>810,39; 1228,21</t>
+          <t>803,46; 1228,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>359,8; 538,2</t>
+          <t>361,7; 537,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>358,03; 521,16</t>
+          <t>353,91; 508,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P74B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P74B-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,74; 79,41</t>
+          <t>71,58; 79,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,14; 65,25</t>
+          <t>55,49; 65,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54,33; 65,17</t>
+          <t>55,05; 65,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457,73; 734,71</t>
+          <t>455,59; 737,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>236,43; 379,3</t>
+          <t>237,5; 388,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>233,54; 408,51</t>
+          <t>238,79; 417,9</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,77; 68,89</t>
+          <t>52,2; 68,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,24; 47,24</t>
+          <t>34,31; 47,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,63; 50,05</t>
+          <t>39,18; 50,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1277,82; 3545,23</t>
+          <t>1266,06; 3732,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>397,89; 857,55</t>
+          <t>384,64; 863,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>374,33; 701,92</t>
+          <t>364,07; 679,93</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,16; 90,87</t>
+          <t>53,39; 91,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,0; 61,62</t>
+          <t>27,05; 64,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,78; 49,18</t>
+          <t>19,07; 50,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>543,28; 2739,32</t>
+          <t>538,46; 2890,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>150,19; 948,02</t>
+          <t>144,22; 939,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99,15; 473,64</t>
+          <t>104,93; 522,01</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,58; 78,49</t>
+          <t>71,72; 78,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,81; 59,48</t>
+          <t>51,53; 58,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,88; 57,34</t>
+          <t>49,86; 57,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>803,46; 1228,43</t>
+          <t>802,34; 1210,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>361,7; 537,45</t>
+          <t>361,99; 529,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>353,91; 508,11</t>
+          <t>355,32; 518,39</t>
         </is>
       </c>
     </row>
